--- a/codelists/myocardial_infarction_raw.xlsx
+++ b/codelists/myocardial_infarction_raw.xlsx
@@ -410,7 +410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S270"/>
+  <dimension ref="A1:S267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.48" customWidth="1" min="1" max="1"/>
@@ -4942,7 +4942,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>300882013</t>
+          <t>299813018</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Gyu36</t>
+          <t>G353</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Gyu3600</t>
+          <t>G353.00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[X]Subsequent myocardial infarction of unspecified site</t>
+          <t>Subsequent myocardial infarction of other sites</t>
         </is>
       </c>
       <c r="H70" s="1" t="n">
@@ -5003,7 +5003,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>299813018</t>
+          <t>300882013</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>G353</t>
+          <t>Gyu36</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>G353.00</t>
+          <t>Gyu3600</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Subsequent myocardial infarction of other sites</t>
+          <t>[X]Subsequent myocardial infarction of unspecified site</t>
         </is>
       </c>
       <c r="H71" s="1" t="n">
@@ -13195,7 +13195,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>408571000006116</t>
+          <t>865021000006111</t>
         </is>
       </c>
       <c r="B227" s="1" t="n">
@@ -13203,34 +13203,34 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Gyu31</t>
+          <t>790H0-97</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Gyu3100</t>
+          <t>790H097</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>302049001</t>
+          <t>585461000000102</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>443587013</t>
+          <t>865021000006111</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>[X]Other current complicatns following acute myocard infarct</t>
+          <t>Heart lesion excision NOS</t>
         </is>
       </c>
       <c r="H227" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I227" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J227" s="1" t="n"/>
       <c r="K227" s="1" t="n"/>
@@ -13246,42 +13246,38 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>865021000006111</t>
+          <t>3024781000006112</t>
         </is>
       </c>
       <c r="B228" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>790H0-97</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>790H097</t>
-        </is>
-      </c>
+          <t>^ESCTPA302478</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>585461000000102</t>
+          <t>32574007</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>865021000006111</t>
+          <t>54388015</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Heart lesion excision NOS</t>
+          <t>Past myocardial infarction diagnosed on ECG AND/OR other special investigation, but currently presenting no symptoms</t>
         </is>
       </c>
       <c r="H228" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I228" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J228" s="1" t="n"/>
       <c r="K228" s="1" t="n"/>
@@ -13297,31 +13293,31 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>3024781000006112</t>
+          <t>4775931000006111</t>
         </is>
       </c>
       <c r="B229" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>^ESCTPA302478</t>
+          <t>^ESCTAB477593</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
-          <t>32574007</t>
+          <t>194821006</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>54388015</t>
+          <t>2619483012</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Past myocardial infarction diagnosed on ECG AND/OR other special investigation, but currently presenting no symptoms</t>
+          <t>Aborted myocardial infarction</t>
         </is>
       </c>
       <c r="H229" s="1" t="n">
@@ -13344,7 +13340,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>4775931000006111</t>
+          <t>5056431000006116</t>
         </is>
       </c>
       <c r="B230" s="1" t="n">
@@ -13352,23 +13348,23 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>^ESCTAB477593</t>
+          <t>^ESCTOL505643</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>194821006</t>
+          <t>233841005</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2619483012</t>
+          <t>350374012</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Aborted myocardial infarction</t>
+          <t>Old lateral myocardial infarction</t>
         </is>
       </c>
       <c r="H230" s="1" t="n">
@@ -13391,7 +13387,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>5056431000006116</t>
+          <t>6969941000006114</t>
         </is>
       </c>
       <c r="B231" s="1" t="n">
@@ -13399,23 +13395,23 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>^ESCTOL505643</t>
+          <t>^ESCTCO696994</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
-          <t>233841005</t>
+          <t>421327009</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>350374012</t>
+          <t>2618027011</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Old lateral myocardial infarction</t>
+          <t>Coronary artery stent thrombosis</t>
         </is>
       </c>
       <c r="H231" s="1" t="n">
@@ -13438,31 +13434,31 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>6969941000006114</t>
+          <t>5605381000006117</t>
         </is>
       </c>
       <c r="B232" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>^ESCTCO696994</t>
+          <t>^ESCTAN560538</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
-          <t>421327009</t>
+          <t>277834005</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2618027011</t>
+          <t>414552014</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Coronary artery stent thrombosis</t>
+          <t>Anxiety about having a heart attack</t>
         </is>
       </c>
       <c r="H232" s="1" t="n">
@@ -13485,7 +13481,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>5605381000006117</t>
+          <t>8087551000006113</t>
         </is>
       </c>
       <c r="B233" s="1" t="n">
@@ -13493,23 +13489,23 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>^ESCTAN560538</t>
+          <t>^ESCTHI808755</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
-          <t>277834005</t>
+          <t>285721000119104</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>414552014</t>
+          <t>3307011019</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Anxiety about having a heart attack</t>
+          <t>History of acute ST segment elevation myocardial infarction</t>
         </is>
       </c>
       <c r="H233" s="1" t="n">
@@ -13532,7 +13528,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>8087551000006113</t>
+          <t>865031000006114</t>
         </is>
       </c>
       <c r="B234" s="1" t="n">
@@ -13540,23 +13536,27 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>^ESCTHI808755</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>790H0-98</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>790H098</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>285721000119104</t>
+          <t>585461000000102</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>3307011019</t>
+          <t>865031000006114</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>History of acute ST segment elevation myocardial infarction</t>
+          <t>Infarct myocardiectomy</t>
         </is>
       </c>
       <c r="H234" s="1" t="n">
@@ -13579,7 +13579,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5902171000006112</t>
+          <t>14194831000006115</t>
         </is>
       </c>
       <c r="B235" s="1" t="n">
@@ -13587,30 +13587,30 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>^ESCTSE590217</t>
+          <t>^ESCT1419483</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
-          <t>302049001</t>
+          <t>776219771000119107</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>1208730013</t>
+          <t>4029332014</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Sequela of disorder</t>
+          <t>History of type 2 myocardial infarction</t>
         </is>
       </c>
       <c r="H235" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I235" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J235" s="1" t="n"/>
       <c r="K235" s="1" t="n"/>
@@ -13626,7 +13626,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>865031000006114</t>
+          <t>14132951000006116</t>
         </is>
       </c>
       <c r="B236" s="1" t="n">
@@ -13634,27 +13634,23 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>790H0-98</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>790H098</t>
-        </is>
-      </c>
+          <t>^ESCT1413295</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
-          <t>585461000000102</t>
+          <t>879955009</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>865031000006114</t>
+          <t>3994017019</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Infarct myocardiectomy</t>
+          <t>MINOCA - myocardial infarction with non-obstructive coronary artery</t>
         </is>
       </c>
       <c r="H236" s="1" t="n">
@@ -13677,38 +13673,42 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>14194831000006115</t>
+          <t>865041000006116</t>
         </is>
       </c>
       <c r="B237" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>^ESCT1419483</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>790H0-99</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>790H099</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>776219771000119107</t>
+          <t>585461000000102</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>4029332014</t>
+          <t>865041000006116</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>History of type 2 myocardial infarction</t>
+          <t>Heart lesion excision</t>
         </is>
       </c>
       <c r="H237" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I237" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J237" s="1" t="n"/>
       <c r="K237" s="1" t="n"/>
@@ -13724,31 +13724,31 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>14132951000006116</t>
+          <t>14145391000006116</t>
         </is>
       </c>
       <c r="B238" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>^ESCT1413295</t>
+          <t>^ESCT1414539</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
-          <t>879955009</t>
+          <t>896691006</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>3994017019</t>
+          <t>4028649016</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>MINOCA - myocardial infarction with non-obstructive coronary artery</t>
+          <t>Acute ST segment elevation myocardial infarction due to occlusion of circumflex branch of left coronary artery</t>
         </is>
       </c>
       <c r="H238" s="1" t="n">
@@ -13771,42 +13771,38 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>865041000006116</t>
+          <t>14742011000006111</t>
         </is>
       </c>
       <c r="B239" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>790H0-99</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>790H099</t>
-        </is>
-      </c>
+          <t>^ESCT1474201</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
-          <t>585461000000102</t>
+          <t>1204155000</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>865041000006116</t>
+          <t>4952482011</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Heart lesion excision</t>
+          <t>Acute anterior non-ST segment elevation myocardial infarction</t>
         </is>
       </c>
       <c r="H239" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I239" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J239" s="1" t="n"/>
       <c r="K239" s="1" t="n"/>
@@ -13822,45 +13818,45 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>14145391000006116</t>
+          <t>4586221000006118</t>
         </is>
       </c>
       <c r="B240" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>^ESCT1414539</t>
+          <t>^ESCTLA458622</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
-          <t>896691006</t>
+          <t>164871004</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>4028649016</t>
+          <t>2692104017</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Acute ST segment elevation myocardial infarction due to occlusion of circumflex branch of left coronary artery</t>
+          <t>Lateral infarction on electrocardiogram</t>
         </is>
       </c>
       <c r="H240" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I240" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="I240" s="1" t="n"/>
       <c r="J240" s="1" t="n"/>
       <c r="K240" s="1" t="n"/>
       <c r="L240" s="1" t="n"/>
       <c r="M240" s="1" t="n"/>
       <c r="N240" s="1" t="n"/>
-      <c r="O240" s="1" t="n"/>
+      <c r="O240" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="P240" s="1" t="n"/>
       <c r="Q240" s="1" t="n"/>
       <c r="R240" s="1" t="n"/>
@@ -13869,7 +13865,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>14742011000006111</t>
+          <t>5056441000006114</t>
         </is>
       </c>
       <c r="B241" s="1" t="n">
@@ -13877,23 +13873,23 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>^ESCT1474201</t>
+          <t>^ESCTOL505644</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
-          <t>1204155000</t>
+          <t>233842003</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>4952482011</t>
+          <t>350375013</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Acute anterior non-ST segment elevation myocardial infarction</t>
+          <t>Old posterior myocardial infarction</t>
         </is>
       </c>
       <c r="H241" s="1" t="n">
@@ -13916,7 +13912,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>4586221000006118</t>
+          <t>3288511000006116</t>
         </is>
       </c>
       <c r="B242" s="1" t="n">
@@ -13924,37 +13920,37 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>^ESCTLA458622</t>
+          <t>^ESCTMI328851</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
-          <t>164871004</t>
+          <t>48724000</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>2692104017</t>
+          <t>1230639015</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Lateral infarction on electrocardiogram</t>
+          <t>MI - Mitral incompetence</t>
         </is>
       </c>
       <c r="H242" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I242" s="1" t="n"/>
+      <c r="I242" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="J242" s="1" t="n"/>
       <c r="K242" s="1" t="n"/>
       <c r="L242" s="1" t="n"/>
       <c r="M242" s="1" t="n"/>
       <c r="N242" s="1" t="n"/>
-      <c r="O242" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O242" s="1" t="n"/>
       <c r="P242" s="1" t="n"/>
       <c r="Q242" s="1" t="n"/>
       <c r="R242" s="1" t="n"/>
@@ -13963,7 +13959,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5056441000006114</t>
+          <t>14194701000006115</t>
         </is>
       </c>
       <c r="B243" s="1" t="n">
@@ -13971,23 +13967,23 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>^ESCTOL505644</t>
+          <t>^ESCT1419470</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
-          <t>233842003</t>
+          <t>726499301000119105</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>350375013</t>
+          <t>4030229011</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Old posterior myocardial infarction</t>
+          <t>Myocardial infarction due to atherothrombotic coronary artery disease</t>
         </is>
       </c>
       <c r="H243" s="1" t="n">
@@ -14010,7 +14006,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>3288511000006116</t>
+          <t>14145371000006117</t>
         </is>
       </c>
       <c r="B244" s="1" t="n">
@@ -14018,23 +14014,23 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>^ESCTMI328851</t>
+          <t>^ESCT1414537</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
-          <t>48724000</t>
+          <t>896689003</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>1230639015</t>
+          <t>4028647019</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>MI - Mitral incompetence</t>
+          <t>Acute myocardial infarction due to occlusion of circumflex branch of left coronary artery</t>
         </is>
       </c>
       <c r="H244" s="1" t="n">
@@ -14057,31 +14053,31 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>14194701000006115</t>
+          <t>14428131000006112</t>
         </is>
       </c>
       <c r="B245" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>^ESCT1419470</t>
+          <t>^ESCT1442813</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
-          <t>726499301000119105</t>
+          <t>1142308000</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>4030229011</t>
+          <t>4537390011</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Myocardial infarction due to atherothrombotic coronary artery disease</t>
+          <t>Mitral valve regurgitation due to acute myocardial infarction</t>
         </is>
       </c>
       <c r="H245" s="1" t="n">
@@ -14104,38 +14100,38 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>14145371000006117</t>
+          <t>3288531000006110</t>
         </is>
       </c>
       <c r="B246" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>^ESCT1414537</t>
+          <t>^ESCTMI328853</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
-          <t>896689003</t>
+          <t>48724000</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>4028647019</t>
+          <t>1230641019</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Acute myocardial infarction due to occlusion of circumflex branch of left coronary artery</t>
+          <t>Mitral insufficiency</t>
         </is>
       </c>
       <c r="H246" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I246" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J246" s="1" t="n"/>
       <c r="K246" s="1" t="n"/>
@@ -14151,7 +14147,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>14428131000006112</t>
+          <t>7848541000006112</t>
         </is>
       </c>
       <c r="B247" s="1" t="n">
@@ -14159,23 +14155,23 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>^ESCT1442813</t>
+          <t>^ESCTAR784854</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>1142308000</t>
+          <t>723860000</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>4537390011</t>
+          <t>3427221011</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Mitral valve regurgitation due to acute myocardial infarction</t>
+          <t>Arrhythmia as current complication following acute myocardial infarction</t>
         </is>
       </c>
       <c r="H247" s="1" t="n">
@@ -14198,38 +14194,38 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>3288531000006110</t>
+          <t>8032161000006112</t>
         </is>
       </c>
       <c r="B248" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>^ESCTMI328853</t>
+          <t>^ESCTCO803216</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
-          <t>48724000</t>
+          <t>103011000119106</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>1230641019</t>
+          <t>3290272012</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Mitral insufficiency</t>
+          <t>Coronary arteriosclerosis in patient with history of previous myocardial infarction</t>
         </is>
       </c>
       <c r="H248" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I248" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J248" s="1" t="n"/>
       <c r="K248" s="1" t="n"/>
@@ -14245,31 +14241,31 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>7848541000006112</t>
+          <t>14752451000006117</t>
         </is>
       </c>
       <c r="B249" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>^ESCTAR784854</t>
+          <t>^ESCT1475245</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>723860000</t>
+          <t>1208867006</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>3427221011</t>
+          <t>5013229011</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Arrhythmia as current complication following acute myocardial infarction</t>
+          <t>Ventricular thrombus following acute myocardial infarction</t>
         </is>
       </c>
       <c r="H249" s="1" t="n">
@@ -14292,7 +14288,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>8032161000006112</t>
+          <t>5056261000006112</t>
         </is>
       </c>
       <c r="B250" s="1" t="n">
@@ -14300,30 +14296,30 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>^ESCTCO803216</t>
+          <t>^ESCTAS505626</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>103011000119106</t>
+          <t>233823002</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>3290272012</t>
+          <t>350356015</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Coronary arteriosclerosis in patient with history of previous myocardial infarction</t>
+          <t>Asymptomatic ischaemia</t>
         </is>
       </c>
       <c r="H250" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I250" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J250" s="1" t="n"/>
       <c r="K250" s="1" t="n"/>
@@ -14339,7 +14335,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>14752451000006117</t>
+          <t>6864791000006113</t>
         </is>
       </c>
       <c r="B251" s="1" t="n">
@@ -14347,23 +14343,23 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>^ESCT1475245</t>
+          <t>^ESCTMY686479</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>1208867006</t>
+          <t>414795007</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>5013229011</t>
+          <t>2534665017</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Ventricular thrombus following acute myocardial infarction</t>
+          <t>Myocardial ischemia</t>
         </is>
       </c>
       <c r="H251" s="1" t="n">
@@ -14386,7 +14382,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>5056261000006112</t>
+          <t>7361481000006115</t>
         </is>
       </c>
       <c r="B252" s="1" t="n">
@@ -14394,37 +14390,37 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>^ESCTAS505626</t>
+          <t>^ESCTTI736148</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
-          <t>233823002</t>
+          <t>448885006</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>350356015</t>
+          <t>2902113016</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Asymptomatic ischaemia</t>
+          <t>Time from arrival at facility to administration of parenteral treatment</t>
         </is>
       </c>
       <c r="H252" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I252" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="I252" s="1" t="n"/>
       <c r="J252" s="1" t="n"/>
       <c r="K252" s="1" t="n"/>
       <c r="L252" s="1" t="n"/>
       <c r="M252" s="1" t="n"/>
       <c r="N252" s="1" t="n"/>
-      <c r="O252" s="1" t="n"/>
+      <c r="O252" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="P252" s="1" t="n"/>
       <c r="Q252" s="1" t="n"/>
       <c r="R252" s="1" t="n"/>
@@ -14433,7 +14429,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>6864791000006113</t>
+          <t>7662871000006115</t>
         </is>
       </c>
       <c r="B253" s="1" t="n">
@@ -14441,23 +14437,23 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>^ESCTMY686479</t>
+          <t>^ESCTIN766287</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>414795007</t>
+          <t>710031008</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2534665017</t>
+          <t>3042814015</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Myocardial ischemia</t>
+          <t>Inducible ischaemia manifest on stress test post myocardial infarction</t>
         </is>
       </c>
       <c r="H253" s="1" t="n">
@@ -14480,7 +14476,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>7361481000006115</t>
+          <t>14194711000006117</t>
         </is>
       </c>
       <c r="B254" s="1" t="n">
@@ -14488,37 +14484,37 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>^ESCTTI736148</t>
+          <t>^ESCT1419471</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
-          <t>448885006</t>
+          <t>726499301000119105</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>2902113016</t>
+          <t>4030227013</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Time from arrival at facility to administration of parenteral treatment</t>
+          <t>Type 1 myocardial infarction</t>
         </is>
       </c>
       <c r="H254" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I254" s="1" t="n"/>
+      <c r="I254" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="J254" s="1" t="n"/>
       <c r="K254" s="1" t="n"/>
       <c r="L254" s="1" t="n"/>
       <c r="M254" s="1" t="n"/>
       <c r="N254" s="1" t="n"/>
-      <c r="O254" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O254" s="1" t="n"/>
       <c r="P254" s="1" t="n"/>
       <c r="Q254" s="1" t="n"/>
       <c r="R254" s="1" t="n"/>
@@ -14527,7 +14523,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>7662871000006115</t>
+          <t>14194821000006118</t>
         </is>
       </c>
       <c r="B255" s="1" t="n">
@@ -14535,23 +14531,23 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>^ESCTIN766287</t>
+          <t>^ESCT1419482</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>710031008</t>
+          <t>776219771000119107</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>3042814015</t>
+          <t>4029334010</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Inducible ischaemia manifest on stress test post myocardial infarction</t>
+          <t>History of myocardial infarction due to demand ischaemia</t>
         </is>
       </c>
       <c r="H255" s="1" t="n">
@@ -14574,7 +14570,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>14194711000006117</t>
+          <t>14145451000006115</t>
         </is>
       </c>
       <c r="B256" s="1" t="n">
@@ -14582,23 +14578,23 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>^ESCT1419471</t>
+          <t>^ESCT1414545</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
-          <t>726499301000119105</t>
+          <t>896696001</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>4030227013</t>
+          <t>4028675017</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Type 1 myocardial infarction</t>
+          <t>Acute STEMI (ST segment elevation myocardial infarction) of apex of heart</t>
         </is>
       </c>
       <c r="H256" s="1" t="n">
@@ -14621,31 +14617,31 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>14194821000006118</t>
+          <t>14546511000006116</t>
         </is>
       </c>
       <c r="B257" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>^ESCT1419482</t>
+          <t>^ESCT1454651</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
-          <t>776219771000119107</t>
+          <t>1163420005</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>4029334010</t>
+          <t>4596779013</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>History of myocardial infarction due to demand ischaemia</t>
+          <t>Postmyocardial infarction pericardial effusion</t>
         </is>
       </c>
       <c r="H257" s="1" t="n">
@@ -14668,31 +14664,31 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>14145451000006115</t>
+          <t>14741971000006110</t>
         </is>
       </c>
       <c r="B258" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>^ESCT1414545</t>
+          <t>^ESCT1474197</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr">
         <is>
-          <t>896696001</t>
+          <t>1204152002</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>4028675017</t>
+          <t>4952475012</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Acute STEMI (ST segment elevation myocardial infarction) of apex of heart</t>
+          <t>Acute inferior non-ST segment elevation myocardial infarction</t>
         </is>
       </c>
       <c r="H258" s="1" t="n">
@@ -14715,7 +14711,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>14546511000006116</t>
+          <t>14488861000006119</t>
         </is>
       </c>
       <c r="B259" s="1" t="n">
@@ -14723,23 +14719,23 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>^ESCT1454651</t>
+          <t>^ESCT1448886</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
-          <t>1163420005</t>
+          <t>16415081000119104</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>4596779013</t>
+          <t>4573825014</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Postmyocardial infarction pericardial effusion</t>
+          <t>Supraventricular tachycardia following acute myocardial infarction</t>
         </is>
       </c>
       <c r="H259" s="1" t="n">
@@ -14762,7 +14758,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>14741971000006110</t>
+          <t>1790731000006117</t>
         </is>
       </c>
       <c r="B260" s="1" t="n">
@@ -14770,32 +14766,32 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>^ESCT1474197</t>
+          <t>JHCCO241</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1204152002</t>
+          <t>1790731000006101</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>4952475012</t>
+          <t>1790731000006117</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Acute inferior non-ST segment elevation myocardial infarction</t>
+          <t>AMI</t>
         </is>
       </c>
       <c r="H260" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I260" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J260" s="1" t="n"/>
+      <c r="I260" s="1" t="n"/>
+      <c r="J260" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="K260" s="1" t="n"/>
       <c r="L260" s="1" t="n"/>
       <c r="M260" s="1" t="n"/>
@@ -14809,7 +14805,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>14488861000006119</t>
+          <t>3166771000006117</t>
         </is>
       </c>
       <c r="B261" s="1" t="n">
@@ -14817,23 +14813,23 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>^ESCT1448886</t>
+          <t>^ESCTRA316677</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>16415081000119104</t>
+          <t>41380003</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>4573825014</t>
+          <t>69025012</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Supraventricular tachycardia following acute myocardial infarction</t>
+          <t>Radioisotope scan for myocardial infarction</t>
         </is>
       </c>
       <c r="H261" s="1" t="n">
@@ -14856,7 +14852,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1790731000006117</t>
+          <t>7107851000006112</t>
         </is>
       </c>
       <c r="B262" s="1" t="n">
@@ -14864,32 +14860,32 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>JHCCO241</t>
+          <t>^ESCTAN710785</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>1790731000006101</t>
+          <t>429731003</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>1790731000006117</t>
+          <t>2695928013</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>AMI</t>
+          <t>Anterior myocardial infarction on electrocardiogram</t>
         </is>
       </c>
       <c r="H262" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I262" s="1" t="n"/>
-      <c r="J262" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="I262" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" s="1" t="n"/>
       <c r="K262" s="1" t="n"/>
       <c r="L262" s="1" t="n"/>
       <c r="M262" s="1" t="n"/>
@@ -14903,7 +14899,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5902181000006110</t>
+          <t>7848501000006110</t>
         </is>
       </c>
       <c r="B263" s="1" t="n">
@@ -14911,30 +14907,30 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>^ESCTSE590218</t>
+          <t>^ESCTVE784850</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
-          <t>302049001</t>
+          <t>723858002</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>443587013</t>
+          <t>3427203013</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Sequelae of disorders</t>
+          <t>Ventricular aneurysm as current complication following acute myocardial infarction</t>
         </is>
       </c>
       <c r="H263" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I263" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J263" s="1" t="n"/>
       <c r="K263" s="1" t="n"/>
@@ -14950,7 +14946,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>3166771000006117</t>
+          <t>7848521000006117</t>
         </is>
       </c>
       <c r="B264" s="1" t="n">
@@ -14958,23 +14954,23 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>^ESCTRA316677</t>
+          <t>^ESCTPU784852</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr">
         <is>
-          <t>41380003</t>
+          <t>723859005</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>69025012</t>
+          <t>3427206017</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Radioisotope scan for myocardial infarction</t>
+          <t>Pulmonary embolism as current complication following acute myocardial infarction</t>
         </is>
       </c>
       <c r="H264" s="1" t="n">
@@ -14997,7 +14993,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>7107851000006112</t>
+          <t>3527838013</t>
         </is>
       </c>
       <c r="B265" s="1" t="n">
@@ -15005,23 +15001,23 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>^ESCTAN710785</t>
+          <t>^ESCT1167751</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
-          <t>429731003</t>
+          <t>737438001</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2695928013</t>
+          <t>3527838013</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Anterior myocardial infarction on electrocardiogram</t>
+          <t>Myocardial infarction clinical management plan</t>
         </is>
       </c>
       <c r="H265" s="1" t="n">
@@ -15044,7 +15040,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>7848501000006110</t>
+          <t>8024001000006117</t>
         </is>
       </c>
       <c r="B266" s="1" t="n">
@@ -15052,23 +15048,23 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>^ESCTVE784850</t>
+          <t>^ESCTAC802400</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
-          <t>723858002</t>
+          <t>78741000119103</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>3427203013</t>
+          <t>2981331011</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Ventricular aneurysm as current complication following acute myocardial infarction</t>
+          <t>Acute coronary artery occlusion not resulting in myocardial infarction</t>
         </is>
       </c>
       <c r="H266" s="1" t="n">
@@ -15091,7 +15087,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>7848521000006117</t>
+          <t>14145431000006110</t>
         </is>
       </c>
       <c r="B267" s="1" t="n">
@@ -15099,23 +15095,23 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>^ESCTPU784852</t>
+          <t>^ESCT1414543</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
-          <t>723859005</t>
+          <t>896696001</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>3427206017</t>
+          <t>4028673012</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Pulmonary embolism as current complication following acute myocardial infarction</t>
+          <t>Acute ST segment elevation myocardial infarction of apex of heart</t>
         </is>
       </c>
       <c r="H267" s="1" t="n">
@@ -15135,147 +15131,6 @@
       <c r="R267" s="1" t="n"/>
       <c r="S267" s="1" t="n"/>
     </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>3527838013</t>
-        </is>
-      </c>
-      <c r="B268" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>^ESCT1167751</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>737438001</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>3527838013</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>Myocardial infarction clinical management plan</t>
-        </is>
-      </c>
-      <c r="H268" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I268" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J268" s="1" t="n"/>
-      <c r="K268" s="1" t="n"/>
-      <c r="L268" s="1" t="n"/>
-      <c r="M268" s="1" t="n"/>
-      <c r="N268" s="1" t="n"/>
-      <c r="O268" s="1" t="n"/>
-      <c r="P268" s="1" t="n"/>
-      <c r="Q268" s="1" t="n"/>
-      <c r="R268" s="1" t="n"/>
-      <c r="S268" s="1" t="n"/>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>8024001000006117</t>
-        </is>
-      </c>
-      <c r="B269" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>^ESCTAC802400</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>78741000119103</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>2981331011</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>Acute coronary artery occlusion not resulting in myocardial infarction</t>
-        </is>
-      </c>
-      <c r="H269" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I269" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J269" s="1" t="n"/>
-      <c r="K269" s="1" t="n"/>
-      <c r="L269" s="1" t="n"/>
-      <c r="M269" s="1" t="n"/>
-      <c r="N269" s="1" t="n"/>
-      <c r="O269" s="1" t="n"/>
-      <c r="P269" s="1" t="n"/>
-      <c r="Q269" s="1" t="n"/>
-      <c r="R269" s="1" t="n"/>
-      <c r="S269" s="1" t="n"/>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>14145431000006110</t>
-        </is>
-      </c>
-      <c r="B270" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>^ESCT1414543</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>896696001</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>4028673012</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>Acute ST segment elevation myocardial infarction of apex of heart</t>
-        </is>
-      </c>
-      <c r="H270" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I270" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J270" s="1" t="n"/>
-      <c r="K270" s="1" t="n"/>
-      <c r="L270" s="1" t="n"/>
-      <c r="M270" s="1" t="n"/>
-      <c r="N270" s="1" t="n"/>
-      <c r="O270" s="1" t="n"/>
-      <c r="P270" s="1" t="n"/>
-      <c r="Q270" s="1" t="n"/>
-      <c r="R270" s="1" t="n"/>
-      <c r="S270" s="1" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/codelists/myocardial_infarction_raw.xlsx
+++ b/codelists/myocardial_infarction_raw.xlsx
@@ -4942,7 +4942,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>299813018</t>
+          <t>300882013</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>G353</t>
+          <t>Gyu36</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>G353.00</t>
+          <t>Gyu3600</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Subsequent myocardial infarction of other sites</t>
+          <t>[X]Subsequent myocardial infarction of unspecified site</t>
         </is>
       </c>
       <c r="H70" s="1" t="n">
@@ -5003,7 +5003,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>300882013</t>
+          <t>299813018</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Gyu36</t>
+          <t>G353</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Gyu3600</t>
+          <t>G353.00</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[X]Subsequent myocardial infarction of unspecified site</t>
+          <t>Subsequent myocardial infarction of other sites</t>
         </is>
       </c>
       <c r="H71" s="1" t="n">

--- a/codelists/myocardial_infarction_raw.xlsx
+++ b/codelists/myocardial_infarction_raw.xlsx
@@ -2744,7 +2744,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>299720018</t>
+          <t>460681000006116</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>G30yz</t>
+          <t>G30X</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>G30yz00</t>
+          <t>G30X.00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Other acute myocardial infarction NOS</t>
+          <t>Acute transmural myocardial infarction of unspecif site</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
@@ -2815,7 +2815,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>460681000006116</t>
+          <t>299720018</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>G30X</t>
+          <t>G30yz</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>G30X.00</t>
+          <t>G30yz00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Acute transmural myocardial infarction of unspecif site</t>
+          <t>Other acute myocardial infarction NOS</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
@@ -4942,7 +4942,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>300882013</t>
+          <t>299813018</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Gyu36</t>
+          <t>G353</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Gyu3600</t>
+          <t>G353.00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[X]Subsequent myocardial infarction of unspecified site</t>
+          <t>Subsequent myocardial infarction of other sites</t>
         </is>
       </c>
       <c r="H70" s="1" t="n">
@@ -5003,7 +5003,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>299813018</t>
+          <t>300882013</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>G353</t>
+          <t>Gyu36</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>G353.00</t>
+          <t>Gyu3600</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Subsequent myocardial infarction of other sites</t>
+          <t>[X]Subsequent myocardial infarction of unspecified site</t>
         </is>
       </c>
       <c r="H71" s="1" t="n">

--- a/codelists/myocardial_infarction_raw.xlsx
+++ b/codelists/myocardial_infarction_raw.xlsx
@@ -2744,7 +2744,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>460681000006116</t>
+          <t>299720018</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>G30X</t>
+          <t>G30yz</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>G30X.00</t>
+          <t>G30yz00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Acute transmural myocardial infarction of unspecif site</t>
+          <t>Other acute myocardial infarction NOS</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
@@ -2815,7 +2815,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>299720018</t>
+          <t>460681000006116</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>G30yz</t>
+          <t>G30X</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>G30yz00</t>
+          <t>G30X.00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Other acute myocardial infarction NOS</t>
+          <t>Acute transmural myocardial infarction of unspecif site</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
@@ -4942,7 +4942,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>300882013</t>
+          <t>299813018</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Gyu36</t>
+          <t>G353</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Gyu3600</t>
+          <t>G353.00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[X]Subsequent myocardial infarction of unspecified site</t>
+          <t>Subsequent myocardial infarction of other sites</t>
         </is>
       </c>
       <c r="H70" s="1" t="n">
@@ -5003,7 +5003,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>299813018</t>
+          <t>300882013</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>G353</t>
+          <t>Gyu36</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>G353.00</t>
+          <t>Gyu3600</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Subsequent myocardial infarction of other sites</t>
+          <t>[X]Subsequent myocardial infarction of unspecified site</t>
         </is>
       </c>
       <c r="H71" s="1" t="n">
